--- a/business_surveys/036_smart_security_access_experience_survey--business_surveys.xlsx
+++ b/business_surveys/036_smart_security_access_experience_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>How often do you use the smart access system?</t>
+          <t>Smart Security Access Form Implementation Survey 10</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Do you like the smart access system?</t>
+          <t>Smart Security Access Form Implementation Survey 13</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>How often do you use the smart access system?</t>
+          <t>Smart Security Access Form Implementation Survey 16</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1309,8 +1309,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_satisfied',_'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'very_satisfied', 'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'somewhat_satisfied',_'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'somewhat_satisfied', 'label': 'Somewhat satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_at_all_satisfied',_'label':_'not_at_all_satisfied'}</t>
+          <t>not_at_all_satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'not_at_all_satisfied', 'label': 'Not at all satisfied'}</t>
+          <t>Not at all satisfied</t>
         </is>
       </c>
     </row>
@@ -1423,12 +1423,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'unsure',_'label':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'unsure', 'label': 'Unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_easy_to_use',_'label':_'very_easy_to_use'}</t>
+          <t>very_easy_to_use</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'very_easy_to_use', 'label': 'Very easy to use'}</t>
+          <t>Very easy to use</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'somewhat_easy_to_use',_'label':_'somewhat_easy_to_use'}</t>
+          <t>somewhat_easy_to_use</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'somewhat_easy_to_use', 'label': 'Somewhat easy to use'}</t>
+          <t>Somewhat easy to use</t>
         </is>
       </c>
     </row>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_at_all_easy_to_use',_'label':_'not_at_all_easy_to_use'}</t>
+          <t>not_at_all_easy_to_use</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'not_at_all_easy_to_use', 'label': 'Not at all easy to use'}</t>
+          <t>Not at all easy to use</t>
         </is>
       </c>
     </row>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'unsure',_'label':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'unsure', 'label': 'Unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
@@ -1508,12 +1508,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_positive',_'label':_'very_positive'}</t>
+          <t>very_positive</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'very_positive', 'label': 'Very positive'}</t>
+          <t>Very positive</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'somewhat_positive',_'label':_'somewhat_positive'}</t>
+          <t>somewhat_positive</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'somewhat_positive', 'label': 'Somewhat positive'}</t>
+          <t>Somewhat positive</t>
         </is>
       </c>
     </row>
@@ -1542,12 +1542,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_at_all_positive',_'label':_'not_at_all_positive'}</t>
+          <t>not_at_all_positive</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'not_at_all_positive', 'label': 'Not at all positive'}</t>
+          <t>Not at all positive</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'unsure',_'label':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'unsure', 'label': 'Unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
@@ -1576,12 +1576,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'less_than_30_days',_'label':_'less_than_30_days'}</t>
+          <t>less_than_30_days</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'less_than_30_days', 'label': 'Less than 30 days'}</t>
+          <t>Less than 30 days</t>
         </is>
       </c>
     </row>
@@ -1593,12 +1593,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'more_than_30_days',_'label':_'more_than_30_days'}</t>
+          <t>more_than_30_days</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'more_than_30_days', 'label': 'More than 30 days'}</t>
+          <t>More than 30 days</t>
         </is>
       </c>
     </row>
@@ -1610,12 +1610,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'unsure',_'label':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'unsure', 'label': 'Unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
@@ -1627,12 +1627,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_easy_to_use',_'label':_'very_easy_to_use'}</t>
+          <t>very_easy_to_use</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'very_easy_to_use', 'label': 'Very easy to use'}</t>
+          <t>Very easy to use</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'somewhat_easy_to_use',_'label':_'somewhat_easy_to_use'}</t>
+          <t>somewhat_easy_to_use</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'somewhat_easy_to_use', 'label': 'Somewhat easy to use'}</t>
+          <t>Somewhat easy to use</t>
         </is>
       </c>
     </row>
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_at_all_easy_to_use',_'label':_'not_at_all_easy_to_use'}</t>
+          <t>not_at_all_easy_to_use</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'not_at_all_easy_to_use', 'label': 'Not at all easy to use'}</t>
+          <t>Not at all easy to use</t>
         </is>
       </c>
     </row>
@@ -1678,12 +1678,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'unsure',_'label':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'unsure', 'label': 'Unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
@@ -1695,12 +1695,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_good',_'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'very_good', 'label': 'Very good'}</t>
+          <t>Very good</t>
         </is>
       </c>
     </row>
@@ -1712,12 +1712,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'somewhat_good',_'label':_'somewhat_good'}</t>
+          <t>somewhat_good</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'somewhat_good', 'label': 'Somewhat good'}</t>
+          <t>Somewhat good</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_at_all_good',_'label':_'not_at_all_good'}</t>
+          <t>not_at_all_good</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'not_at_all_good', 'label': 'Not at all good'}</t>
+          <t>Not at all good</t>
         </is>
       </c>
     </row>
@@ -1746,12 +1746,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'unsure',_'label':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'unsure', 'label': 'Unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
@@ -1763,12 +1763,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_easy_to_get_help',_'label':_'very_easy_to_get_help'}</t>
+          <t>very_easy_to_get_help</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'very_easy_to_get_help', 'label': 'Very easy to get help'}</t>
+          <t>Very easy to get help</t>
         </is>
       </c>
     </row>
@@ -1780,12 +1780,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'somewhat_easy_to_get_help',_'label':_'somewhat_easy_to_get_help'}</t>
+          <t>somewhat_easy_to_get_help</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'somewhat_easy_to_get_help', 'label': 'Somewhat easy to get help'}</t>
+          <t>Somewhat easy to get help</t>
         </is>
       </c>
     </row>
@@ -1797,12 +1797,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_at_all_easy_to_get_help',_'label':_'not_at_all_easy_to_get_help'}</t>
+          <t>not_at_all_easy_to_get_help</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'not_at_all_easy_to_get_help', 'label': 'Not at all easy to get help'}</t>
+          <t>Not at all easy to get help</t>
         </is>
       </c>
     </row>
@@ -1814,12 +1814,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'unsure',_'label':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'unsure', 'label': 'Unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
@@ -1831,12 +1831,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_likely_to_use',_'label':_'very_likely_to_use'}</t>
+          <t>very_likely_to_use</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'very_likely_to_use', 'label': 'Very likely to use'}</t>
+          <t>Very likely to use</t>
         </is>
       </c>
     </row>
@@ -1848,12 +1848,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'somewhat_likely_to_use',_'label':_'somewhat_likely_to_use'}</t>
+          <t>somewhat_likely_to_use</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'somewhat_likely_to_use', 'label': 'Somewhat likely to use'}</t>
+          <t>Somewhat likely to use</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_at_all_likely_to_use',_'label':_'not_at_all_likely_to_use'}</t>
+          <t>not_at_all_likely_to_use</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'not_at_all_likely_to_use', 'label': 'Not at all likely to use'}</t>
+          <t>Not at all likely to use</t>
         </is>
       </c>
     </row>
@@ -1882,12 +1882,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'unsure',_'label':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'unsure', 'label': 'Unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
@@ -1899,12 +1899,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_frequently',_'label':_'very_frequently'}</t>
+          <t>very_frequently</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'very_frequently', 'label': 'Very frequently'}</t>
+          <t>Very frequently</t>
         </is>
       </c>
     </row>
@@ -1916,12 +1916,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'somewhat_frequently',_'label':_'somewhat_frequently'}</t>
+          <t>somewhat_frequently</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'somewhat_frequently', 'label': 'Somewhat frequently'}</t>
+          <t>Somewhat frequently</t>
         </is>
       </c>
     </row>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_at_all_frequently',_'label':_'not_at_all_frequently'}</t>
+          <t>not_at_all_frequently</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'not_at_all_frequently', 'label': 'Not at all frequently'}</t>
+          <t>Not at all frequently</t>
         </is>
       </c>
     </row>
@@ -1950,12 +1950,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'unsure',_'label':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'unsure', 'label': 'Unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
@@ -1967,12 +1967,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2001,12 +2001,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'unsure',_'label':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'unsure', 'label': 'Unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
@@ -2018,12 +2018,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2035,12 +2035,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2052,12 +2052,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'unsure',_'label':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'unsure', 'label': 'Unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
@@ -2069,12 +2069,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_positive',_'label':_'very_positive'}</t>
+          <t>very_positive</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'very_positive', 'label': 'Very positive'}</t>
+          <t>Very positive</t>
         </is>
       </c>
     </row>
@@ -2086,12 +2086,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'somewhat_positive',_'label':_'somewhat_positive'}</t>
+          <t>somewhat_positive</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'somewhat_positive', 'label': 'Somewhat positive'}</t>
+          <t>Somewhat positive</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_at_all_positive',_'label':_'not_at_all_positive'}</t>
+          <t>not_at_all_positive</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'not_at_all_positive', 'label': 'Not at all positive'}</t>
+          <t>Not at all positive</t>
         </is>
       </c>
     </row>
@@ -2120,12 +2120,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'unsure',_'label':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'unsure', 'label': 'Unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
@@ -2137,12 +2137,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2171,12 +2171,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'unsure',_'label':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'unsure', 'label': 'Unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
@@ -2188,12 +2188,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_frequently',_'label':_'very_frequently'}</t>
+          <t>very_frequently</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'very_frequently', 'label': 'Very frequently'}</t>
+          <t>Very frequently</t>
         </is>
       </c>
     </row>
@@ -2205,12 +2205,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'somewhat_frequently',_'label':_'somewhat_frequently'}</t>
+          <t>somewhat_frequently</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'somewhat_frequently', 'label': 'Somewhat frequently'}</t>
+          <t>Somewhat frequently</t>
         </is>
       </c>
     </row>
@@ -2222,12 +2222,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_at_all_frequently',_'label':_'not_at_all_frequently'}</t>
+          <t>not_at_all_frequently</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'not_at_all_frequently', 'label': 'Not at all frequently'}</t>
+          <t>Not at all frequently</t>
         </is>
       </c>
     </row>
@@ -2239,12 +2239,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'unsure',_'label':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'unsure', 'label': 'Unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
@@ -2256,12 +2256,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2273,12 +2273,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2290,12 +2290,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'unsure',_'label':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'unsure', 'label': 'Unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
@@ -2307,12 +2307,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_easy_to_find',_'label':_'very_easy_to_find'}</t>
+          <t>very_easy_to_find</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'very_easy_to_find', 'label': 'Very easy to find'}</t>
+          <t>Very easy to find</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'somewhat_easy_to_find',_'label':_'somewhat_easy_to_find'}</t>
+          <t>somewhat_easy_to_find</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'somewhat_easy_to_find', 'label': 'Somewhat easy to find'}</t>
+          <t>Somewhat easy to find</t>
         </is>
       </c>
     </row>
@@ -2341,12 +2341,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_at_all_easy_to_find',_'label':_'not_at_all_easy_to_find'}</t>
+          <t>not_at_all_easy_to_find</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'not_at_all_easy_to_find', 'label': 'Not at all easy to find'}</t>
+          <t>Not at all easy to find</t>
         </is>
       </c>
     </row>
@@ -2358,12 +2358,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'unsure',_'label':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'unsure', 'label': 'Unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
@@ -2375,12 +2375,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2392,12 +2392,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2409,12 +2409,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'unsure',_'label':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'unsure', 'label': 'Unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
@@ -2426,12 +2426,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_easy_to_use',_'label':_'very_easy_to_use'}</t>
+          <t>very_easy_to_use</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'very_easy_to_use', 'label': 'Very easy to use'}</t>
+          <t>Very easy to use</t>
         </is>
       </c>
     </row>
@@ -2443,12 +2443,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'somewhat_easy_to_use',_'label':_'somewhat_easy_to_use'}</t>
+          <t>somewhat_easy_to_use</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'somewhat_easy_to_use', 'label': 'Somewhat easy to use'}</t>
+          <t>Somewhat easy to use</t>
         </is>
       </c>
     </row>
@@ -2460,12 +2460,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_at_all_easy_to_use',_'label':_'not_at_all_easy_to_use'}</t>
+          <t>not_at_all_easy_to_use</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'not_at_all_easy_to_use', 'label': 'Not at all easy to use'}</t>
+          <t>Not at all easy to use</t>
         </is>
       </c>
     </row>
@@ -2477,12 +2477,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'unsure',_'label':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'unsure', 'label': 'Unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
@@ -2494,12 +2494,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2511,12 +2511,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2528,12 +2528,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'unsure',_'label':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'unsure', 'label': 'Unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
@@ -2545,12 +2545,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_frequently',_'label':_'very_frequently'}</t>
+          <t>very_frequently</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'very_frequently', 'label': 'Very frequently'}</t>
+          <t>Very frequently</t>
         </is>
       </c>
     </row>
@@ -2562,12 +2562,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'somewhat_frequently',_'label':_'somewhat_frequently'}</t>
+          <t>somewhat_frequently</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'somewhat_frequently', 'label': 'Somewhat frequently'}</t>
+          <t>Somewhat frequently</t>
         </is>
       </c>
     </row>
@@ -2579,12 +2579,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_at_all_frequently',_'label':_'not_at_all_frequently'}</t>
+          <t>not_at_all_frequently</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'not_at_all_frequently', 'label': 'Not at all frequently'}</t>
+          <t>Not at all frequently</t>
         </is>
       </c>
     </row>
@@ -2596,12 +2596,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'unsure',_'label':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'unsure', 'label': 'Unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
@@ -2613,12 +2613,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_easy_to_use',_'label':_'very_easy_to_use'}</t>
+          <t>very_easy_to_use</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'very_easy_to_use', 'label': 'Very easy to use'}</t>
+          <t>Very easy to use</t>
         </is>
       </c>
     </row>
@@ -2630,12 +2630,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'somewhat_easy_to_use',_'label':_'somewhat_easy_to_use'}</t>
+          <t>somewhat_easy_to_use</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'somewhat_easy_to_use', 'label': 'Somewhat easy to use'}</t>
+          <t>Somewhat easy to use</t>
         </is>
       </c>
     </row>
@@ -2647,12 +2647,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_at_all_easy_to_use',_'label':_'not_at_all_easy_to_use'}</t>
+          <t>not_at_all_easy_to_use</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'not_at_all_easy_to_use', 'label': 'Not at all easy to use'}</t>
+          <t>Not at all easy to use</t>
         </is>
       </c>
     </row>
@@ -2664,12 +2664,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'unsure',_'label':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'unsure', 'label': 'Unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
@@ -2715,12 +2715,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2732,12 +2732,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2749,12 +2749,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'unsure',_'label':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'unsure', 'label': 'Unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
@@ -2766,12 +2766,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2800,12 +2800,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'unsure',_'label':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'unsure', 'label': 'Unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
@@ -2817,12 +2817,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2834,12 +2834,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2851,12 +2851,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'unsure',_'label':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'unsure', 'label': 'Unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
